--- a/key.xlsx
+++ b/key.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{740E4E0C-E8E2-4BAD-9F49-9DD9D04B6800}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F869BA65-6EC5-4A56-91B5-2B8933D4B298}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{42E5B6E4-6B5E-43F1-83AD-00E76D3338A8}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="243">
   <si>
     <t>1. safaricom files contain the below fields . Relevant columns for reporting in the 2nd column of the table</t>
   </si>
@@ -750,6 +750,24 @@
   </si>
   <si>
     <t>ADAMS</t>
+  </si>
+  <si>
+    <t>NAKURU SECTION 58</t>
+  </si>
+  <si>
+    <t>NAKURU KENYATTA AVENUE</t>
+  </si>
+  <si>
+    <t>NAKURU SEC 58</t>
+  </si>
+  <si>
+    <t>KENYATTA AVENUE</t>
+  </si>
+  <si>
+    <t>Quick Mart Ltd Nakuru Kenyatta Ave</t>
+  </si>
+  <si>
+    <t>Quick Mark Ltd Nakuru Section 58</t>
   </si>
 </sst>
 </file>
@@ -1412,7 +1430,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45CFE9D2-2FEC-492B-9E7C-039CD064DA0B}">
-  <dimension ref="A2:F236"/>
+  <dimension ref="A2:F240"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="29.6328125" bestFit="1" customWidth="1"/>
@@ -3129,18 +3147,18 @@
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A233" t="s">
+      <c r="A233" s="24" t="s">
         <v>231</v>
       </c>
-      <c r="B233" t="s">
+      <c r="B233" s="24" t="s">
         <v>232</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A234" t="s">
+      <c r="A234" s="24" t="s">
         <v>232</v>
       </c>
-      <c r="B234" t="s">
+      <c r="B234" s="24" t="s">
         <v>233</v>
       </c>
     </row>
@@ -3158,6 +3176,40 @@
       </c>
       <c r="B236" t="s">
         <v>236</v>
+      </c>
+    </row>
+    <row r="237" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A237" t="s">
+        <v>242</v>
+      </c>
+      <c r="B237" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="238" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A238" t="str">
+        <f>B237</f>
+        <v>NAKURU SECTION 58</v>
+      </c>
+      <c r="B238" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="239" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A239" t="s">
+        <v>241</v>
+      </c>
+      <c r="B239" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="240" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A240" t="str">
+        <f>B239</f>
+        <v>NAKURU KENYATTA AVENUE</v>
+      </c>
+      <c r="B240" t="s">
+        <v>240</v>
       </c>
     </row>
   </sheetData>
